--- a/data/trans_dic/P04D$colectiva-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P04D$colectiva-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene calefacción colectiva en su vivienda</t>
+          <t>Población que, al menos, tiene calefacción colectiva en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,37 +678,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,58</t>
+          <t>1,21; 5,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 10,53</t>
+          <t>0,94; 10,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,92</t>
+          <t>0,34; 3,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,67</t>
+          <t>0,79; 5,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,22</t>
+          <t>0,83; 3,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 6,41</t>
+          <t>1,23; 5,93</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,7</t>
+          <t>1,75; 4,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,84</t>
+          <t>0,2; 1,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,95</t>
+          <t>0,97; 5,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,57</t>
+          <t>1,44; 4,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,62</t>
+          <t>0,42; 2,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,89</t>
+          <t>0,43; 2,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,16</t>
+          <t>1,91; 3,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,76</t>
+          <t>0,42; 1,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,09</t>
+          <t>0,89; 3,18</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,37</t>
+          <t>0,58; 3,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,1</t>
+          <t>1,14; 5,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,9; 12,38</t>
+          <t>6,29; 12,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,7</t>
+          <t>0,31; 4,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,95</t>
+          <t>0,85; 3,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,09; 14,97</t>
+          <t>9,01; 15,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,67</t>
+          <t>0,72; 2,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,87</t>
+          <t>1,31; 3,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,42; 12,9</t>
+          <t>8,28; 12,75</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,61; 8,51</t>
+          <t>3,58; 8,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 7,09</t>
+          <t>2,73; 6,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,67; 15,97</t>
+          <t>7,83; 15,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 6,05</t>
+          <t>2,01; 5,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 8,07</t>
+          <t>2,96; 8,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,43; 10,54</t>
+          <t>4,71; 10,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,27; 6,35</t>
+          <t>3,32; 6,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,76</t>
+          <t>3,23; 6,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,65; 11,78</t>
+          <t>6,28; 11,25</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,45; 16,34</t>
+          <t>7,63; 16,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,24; 17,39</t>
+          <t>7,84; 17,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,51</t>
+          <t>0,0; 1,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,05; 15,31</t>
+          <t>9,25; 15,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,46</t>
+          <t>0,0; 0,61</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,59; 8,12</t>
+          <t>2,66; 8,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,28; 19,47</t>
+          <t>10,84; 19,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22,97; 33,56</t>
+          <t>23,15; 34,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,74</t>
+          <t>1,4; 6,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,21; 14,13</t>
+          <t>6,9; 14,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,01; 35,55</t>
+          <t>25,94; 36,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,58; 5,99</t>
+          <t>2,44; 5,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,69; 15,44</t>
+          <t>9,77; 15,51</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26,15; 33,09</t>
+          <t>26,22; 33,21</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,61</t>
+          <t>0,27; 1,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,37</t>
+          <t>2,13; 5,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,13; 8,0</t>
+          <t>4,06; 7,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,3</t>
+          <t>0,14; 1,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,67</t>
+          <t>1,96; 4,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,69</t>
+          <t>1,76; 6,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,17</t>
+          <t>0,26; 1,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,42</t>
+          <t>2,36; 4,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,52</t>
+          <t>2,98; 6,65</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,32</t>
+          <t>1,27; 3,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,61</t>
+          <t>0,25; 1,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,43</t>
+          <t>0,14; 1,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,9</t>
+          <t>1,52; 3,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,27</t>
+          <t>0,13; 1,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,99</t>
+          <t>0,73; 2,07</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,25</t>
+          <t>1,66; 3,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,13</t>
+          <t>0,3; 1,15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,45</t>
+          <t>0,42; 1,44</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,55; 3,78</t>
+          <t>2,57; 3,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,41</t>
+          <t>2,26; 3,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,55; 6,9</t>
+          <t>4,52; 6,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,33</t>
+          <t>2,16; 3,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,02</t>
+          <t>1,98; 3,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,77; 6,68</t>
+          <t>4,74; 6,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,5; 3,33</t>
+          <t>2,54; 3,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,04</t>
+          <t>2,26; 3,05</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,02; 6,51</t>
+          <t>4,99; 6,51</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene calefacción colectiva en su vivienda</t>
+          <t>Población que, al menos, tiene calefacción colectiva en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3619; 16353</t>
+          <t>3543; 15507</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2112</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2663; 32792</t>
+          <t>2923; 31850</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>948; 8351</t>
+          <t>971; 9221</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4300</t>
+          <t>0; 4496</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2392; 13513</t>
+          <t>2300; 14735</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4908; 18622</t>
+          <t>4786; 18883</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4542</t>
+          <t>0; 4556</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7144; 38554</t>
+          <t>7376; 35647</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8286; 23665</t>
+          <t>8827; 23937</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1018; 9236</t>
+          <t>1006; 8424</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4503; 25647</t>
+          <t>5009; 27483</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8248; 23840</t>
+          <t>7525; 23055</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2168; 13703</t>
+          <t>2173; 13150</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2131; 9734</t>
+          <t>2212; 10704</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19705; 42638</t>
+          <t>19626; 40393</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4433; 18064</t>
+          <t>4345; 17816</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8991; 31917</t>
+          <t>9199; 32889</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1862; 10924</t>
+          <t>1882; 9925</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3645; 16248</t>
+          <t>3623; 16684</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18578; 38988</t>
+          <t>19823; 40186</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1073; 12604</t>
+          <t>1073; 13645</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2792; 13277</t>
+          <t>2858; 13317</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31616; 52069</t>
+          <t>31358; 52721</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4530; 17744</t>
+          <t>4807; 18935</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8527; 25371</t>
+          <t>8571; 23784</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>55828; 85500</t>
+          <t>54920; 84503</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13468; 31749</t>
+          <t>13339; 32867</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10103; 26228</t>
+          <t>10115; 25658</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23960; 49912</t>
+          <t>24466; 48523</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8299; 23532</t>
+          <t>7830; 22057</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11215; 31243</t>
+          <t>11462; 31370</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20982; 49920</t>
+          <t>22309; 49081</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24895; 48368</t>
+          <t>25286; 49522</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25328; 51218</t>
+          <t>24439; 50552</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52279; 92563</t>
+          <t>49363; 88437</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15840; 34734</t>
+          <t>16227; 35708</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 1903</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1225</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18095; 38197</t>
+          <t>17219; 38693</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5490</t>
+          <t>0; 4336</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 2533</t>
+          <t>0; 2511</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39117; 66181</t>
+          <t>39969; 67440</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 5109</t>
+          <t>0; 4262</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 2032</t>
+          <t>0; 2671</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7095; 22255</t>
+          <t>7290; 22343</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>27046; 51232</t>
+          <t>28513; 50759</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>61923; 90480</t>
+          <t>62417; 91705</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3996; 16010</t>
+          <t>3918; 16738</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19700; 38587</t>
+          <t>18858; 38622</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>66861; 91372</t>
+          <t>66690; 93187</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14253; 33151</t>
+          <t>13500; 33106</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>51938; 82812</t>
+          <t>52371; 83192</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>137712; 174298</t>
+          <t>138089; 174904</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1764; 10679</t>
+          <t>1760; 9887</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>14228; 35282</t>
+          <t>13971; 35670</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25640; 49685</t>
+          <t>25197; 48628</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>944; 8986</t>
+          <t>943; 8867</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>13690; 32254</t>
+          <t>13565; 32438</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16279; 56570</t>
+          <t>14862; 55891</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3846; 15845</t>
+          <t>3495; 14358</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>31112; 59614</t>
+          <t>31857; 60244</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>47133; 95683</t>
+          <t>43764; 97521</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>9977; 25801</t>
+          <t>9858; 25853</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1906; 12512</t>
+          <t>1963; 12828</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1595; 13254</t>
+          <t>1315; 12573</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>13387; 32153</t>
+          <t>12536; 30023</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1175; 10529</t>
+          <t>1085; 9828</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5108; 14278</t>
+          <t>5224; 14869</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26417; 51950</t>
+          <t>26517; 50133</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4708; 18197</t>
+          <t>4849; 18497</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>8150; 23761</t>
+          <t>6980; 23714</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>87160; 129163</t>
+          <t>87767; 130727</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>76959; 115788</t>
+          <t>76700; 116207</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>157265; 238211</t>
+          <t>156025; 240011</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>76214; 118292</t>
+          <t>76675; 117981</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>70912; 107083</t>
+          <t>70305; 107476</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>176683; 247518</t>
+          <t>175549; 242422</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>174013; 232053</t>
+          <t>177222; 234637</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>157173; 211025</t>
+          <t>156731; 211574</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>359613; 465817</t>
+          <t>357292; 466268</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P04D$colectiva-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P04D$colectiva-Provincia-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 5,29</t>
+          <t>0,98; 5,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -688,37 +688,37 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 10,23</t>
+          <t>0,69; 5,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,22</t>
+          <t>0,34; 2,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 5,09</t>
+          <t>0,93; 5,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,26</t>
+          <t>0,84; 3,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,78</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 5,93</t>
+          <t>1,16; 4,74</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,75</t>
+          <t>1,76; 4,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,37 +798,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,3</t>
+          <t>0,91; 4,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,42</t>
+          <t>1,55; 4,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,51</t>
+          <t>0,58; 2,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,08</t>
+          <t>0,39; 1,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 3,94</t>
+          <t>1,93; 4,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,74</t>
+          <t>0,5; 1,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,18</t>
+          <t>0,79; 2,92</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,06</t>
+          <t>0,58; 3,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,24</t>
+          <t>1,08; 4,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,29; 12,76</t>
+          <t>6,4; 12,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,0</t>
+          <t>0,55; 4,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,96</t>
+          <t>0,85; 4,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,01; 15,15</t>
+          <t>8,65; 14,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,85</t>
+          <t>0,72; 2,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,63</t>
+          <t>1,32; 3,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,28; 12,75</t>
+          <t>8,27; 12,59</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,58; 8,81</t>
+          <t>3,59; 8,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 6,94</t>
+          <t>2,8; 7,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,83; 15,52</t>
+          <t>6,68; 13,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 5,67</t>
+          <t>1,99; 5,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,96; 8,1</t>
+          <t>3,02; 8,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 10,37</t>
+          <t>6,76; 11,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,5</t>
+          <t>3,32; 6,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,68</t>
+          <t>3,29; 6,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,28; 11,25</t>
+          <t>7,62; 12,07</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,63; 16,79</t>
+          <t>7,18; 16,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1133,32 +1133,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,84; 17,62</t>
+          <t>8,2; 17,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,98</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,97</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,25; 15,6</t>
+          <t>8,93; 15,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,99</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,61</t>
+          <t>0,0; 0,58</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>28,45%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,66; 8,15</t>
+          <t>2,63; 8,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,84; 19,29</t>
+          <t>10,55; 19,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23,15; 34,01</t>
+          <t>22,16; 31,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,4; 6,0</t>
+          <t>1,43; 5,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,9; 14,14</t>
+          <t>6,76; 14,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,94; 36,25</t>
+          <t>25,56; 35,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,99</t>
+          <t>2,54; 5,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,77; 15,51</t>
+          <t>9,72; 15,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26,22; 33,21</t>
+          <t>24,82; 31,93</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,49</t>
+          <t>0,26; 1,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,13; 5,43</t>
+          <t>2,14; 5,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,06; 7,83</t>
+          <t>4,95; 8,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,28</t>
+          <t>0,14; 1,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,69</t>
+          <t>1,99; 4,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,76; 6,61</t>
+          <t>4,39; 7,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,06</t>
+          <t>0,28; 1,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,36; 4,47</t>
+          <t>2,44; 4,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,98; 6,65</t>
+          <t>5,04; 7,47</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,33</t>
+          <t>1,18; 3,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,65</t>
+          <t>0,24; 1,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,36</t>
+          <t>0,31; 1,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,64</t>
+          <t>1,52; 3,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,19</t>
+          <t>0,14; 1,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,07</t>
+          <t>0,73; 2,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,13</t>
+          <t>1,68; 3,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,15</t>
+          <t>0,3; 1,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,44</t>
+          <t>0,66; 1,59</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,57; 3,82</t>
+          <t>2,52; 3,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,42</t>
+          <t>2,3; 3,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,52; 6,95</t>
+          <t>5,14; 6,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,32</t>
+          <t>2,13; 3,29</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,03</t>
+          <t>2,01; 3,06</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,74; 6,54</t>
+          <t>5,44; 6,84</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,54; 3,36</t>
+          <t>2,54; 3,41</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,05</t>
+          <t>2,27; 3,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,99; 6,51</t>
+          <t>5,46; 6,56</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5533</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16052</t>
+          <t>14532</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3543; 15507</t>
+          <t>2860; 14999</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1871,37 +1871,37 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2923; 31850</t>
+          <t>2213; 18817</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>971; 9221</t>
+          <t>972; 8477</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4496</t>
+          <t>0; 5329</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2300; 14735</t>
+          <t>2943; 17267</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4786; 18883</t>
+          <t>4885; 18522</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4556</t>
+          <t>0; 5158</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7376; 35647</t>
+          <t>7374; 30095</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11862</t>
+          <t>11165</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5113</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>16975</t>
+          <t>16264</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8827; 23937</t>
+          <t>8844; 24337</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1006; 8424</t>
+          <t>1008; 8460</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5009; 27483</t>
+          <t>4829; 24666</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7525; 23055</t>
+          <t>8073; 23546</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2173; 13150</t>
+          <t>3048; 14148</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2212; 10704</t>
+          <t>2135; 9933</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19626; 40393</t>
+          <t>19793; 42084</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4345; 17816</t>
+          <t>5139; 17217</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9199; 32889</t>
+          <t>8511; 31503</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28178</t>
+          <t>28418</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40738</t>
+          <t>40642</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>68916</t>
+          <t>69060</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1882; 9925</t>
+          <t>1879; 11636</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3623; 16684</t>
+          <t>3438; 15247</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19823; 40186</t>
+          <t>20163; 39758</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1073; 13645</t>
+          <t>1876; 14593</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2858; 13317</t>
+          <t>2846; 13713</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31358; 52721</t>
+          <t>30718; 52437</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4807; 18935</t>
+          <t>4822; 18423</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8571; 23784</t>
+          <t>8633; 25692</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>54920; 84503</t>
+          <t>55396; 84368</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34531</t>
+          <t>36074</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35931</t>
+          <t>39183</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>70462</t>
+          <t>75257</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13339; 32867</t>
+          <t>13389; 30910</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10115; 25658</t>
+          <t>10363; 26540</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24466; 48523</t>
+          <t>24918; 50518</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7830; 22057</t>
+          <t>7737; 21392</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11462; 31370</t>
+          <t>11683; 32740</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22309; 49081</t>
+          <t>28303; 49662</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25286; 49522</t>
+          <t>25281; 48367</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24439; 50552</t>
+          <t>24907; 49910</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>49363; 88437</t>
+          <t>60313; 95578</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>440</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>440</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>16227; 35708</t>
+          <t>15272; 34822</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2528,32 +2528,32 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17219; 38693</t>
+          <t>18002; 38024</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4336</t>
+          <t>0; 4290</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 2511</t>
+          <t>0; 2261</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39969; 67440</t>
+          <t>38580; 65360</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4262</t>
+          <t>0; 5055</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 2671</t>
+          <t>0; 2517</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>75954</t>
+          <t>72165</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79474</t>
+          <t>79902</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>155428</t>
+          <t>152067</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7290; 22343</t>
+          <t>7214; 22799</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>28513; 50759</t>
+          <t>27751; 50157</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>62417; 91705</t>
+          <t>59998; 86171</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3918; 16738</t>
+          <t>3986; 16587</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18858; 38622</t>
+          <t>18474; 38549</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>66690; 93187</t>
+          <t>67426; 93403</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13500; 33106</t>
+          <t>14040; 33009</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>52371; 83192</t>
+          <t>52116; 82469</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>138089; 174904</t>
+          <t>132673; 170666</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>36914</t>
+          <t>46233</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38603</t>
+          <t>44395</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>75518</t>
+          <t>90627</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1760; 9887</t>
+          <t>1755; 11036</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>13971; 35670</t>
+          <t>14032; 34446</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25197; 48628</t>
+          <t>35275; 61606</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>943; 8867</t>
+          <t>946; 8412</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>13565; 32438</t>
+          <t>13741; 31822</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14862; 55891</t>
+          <t>33691; 58013</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3495; 14358</t>
+          <t>3786; 15334</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>31857; 60244</t>
+          <t>32830; 59929</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>43764; 97521</t>
+          <t>74674; 110601</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5582</t>
+          <t>6150</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9142</t>
+          <t>10972</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>14724</t>
+          <t>17121</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>9858; 25853</t>
+          <t>9162; 26353</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1963; 12828</t>
+          <t>1898; 12877</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1315; 12573</t>
+          <t>2453; 13872</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12536; 30023</t>
+          <t>12554; 30511</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1085; 9828</t>
+          <t>1156; 10806</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5224; 14869</t>
+          <t>6108; 17281</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26517; 50133</t>
+          <t>26867; 50790</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4849; 18497</t>
+          <t>4878; 18006</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6980; 23714</t>
+          <t>10746; 25852</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>203541</t>
+          <t>207080</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>214947</t>
+          <t>228289</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>418488</t>
+          <t>435368</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>87767; 130727</t>
+          <t>86186; 129469</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>76700; 116207</t>
+          <t>77926; 115937</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>156025; 240011</t>
+          <t>181171; 236711</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>76675; 117981</t>
+          <t>75749; 116826</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>70305; 107476</t>
+          <t>71198; 108427</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>175549; 242422</t>
+          <t>202710; 254958</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>177222; 234637</t>
+          <t>177480; 238128</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>156731; 211574</t>
+          <t>157320; 213105</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>357292; 466268</t>
+          <t>396060; 475223</t>
         </is>
       </c>
     </row>
